--- a/testdata/xlsx/charts.xlsx
+++ b/testdata/xlsx/charts.xlsx
@@ -1383,6 +1383,17 @@
     <dispBlanksAs val="gap"/>
   </chart>
 </chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="15">
+  <a:schemeClr val="accent6"/>
+  <a:schemeClr val="accent5"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+</cs:colorStyle>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
